--- a/docs/donjons.xlsx
+++ b/docs/donjons.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
   <si>
     <t>Tableau 1</t>
   </si>
@@ -98,7 +98,10 @@
     <t>100</t>
   </si>
   <si>
-    <t>100 EXP + 100 PO + 1 PARCHEMIN</t>
+    <t>200 OR
+100 EXP
+2 PARCHEMINS
+1 EQUIP</t>
   </si>
   <si>
     <t>SOMBRE FORET</t>
@@ -122,7 +125,10 @@
     <t>90,10</t>
   </si>
   <si>
-    <t>150 EXP + 150 PO + 2 PARCHEMIN</t>
+    <t>300 OR
+120 EXP
+2 PARCHEMINS
+1 EQUIP</t>
   </si>
   <si>
     <t>MER SOUTERRAINE</t>
@@ -149,7 +155,10 @@
     <t>80,20</t>
   </si>
   <si>
-    <t>210 EXP + 210 PO + 2 PARCHEMIN</t>
+    <t>420OR
+180 EXP
+2 PARCHEMINS
+2 EQUIP</t>
   </si>
   <si>
     <t>DESERT ARIDE</t>
@@ -173,7 +182,10 @@
     <t>70,30</t>
   </si>
   <si>
-    <t>300 EXP + 300 PO + 3 PARCHEMIN</t>
+    <t>600 OR
+250 EXP
+3 PARCHEMINS
+2 EQUIP</t>
   </si>
   <si>
     <t>TEMPLE ABANDONNE</t>
@@ -200,7 +212,11 @@
     <t>60,35,5</t>
   </si>
   <si>
-    <t>400 EXP + 400 PO + 4 PARCHEMIN</t>
+    <t>800 OR
+360 EXP
+10 PARCHEMINS
+3 EQUIP
+10 TOME D’EXP *</t>
   </si>
   <si>
     <t>CITE MAUDITE</t>
@@ -224,7 +240,10 @@
     <t>55,38,7</t>
   </si>
   <si>
-    <t>550 EXP + 550 PO + 6 PARCHEMIN</t>
+    <t>1100 OR
+450 EXP
+4 PARCHEMINS
+3 EQUIP</t>
   </si>
   <si>
     <t>PALAIS DU ROI DECHU</t>
@@ -248,7 +267,10 @@
     <t>53,39,8</t>
   </si>
   <si>
-    <t>800 EXP + 800 PO + 8 PARCHEMIN</t>
+    <t>1600 OR
+660 EXP
+4 PARCHEMINS
+3 EQUIP</t>
   </si>
   <si>
     <t>CATACOMBES ROYALES</t>
@@ -269,7 +291,10 @@
     <t>50,40,10</t>
   </si>
   <si>
-    <t>1000 EXP + 1000 PO + 10 PARCHEMIN</t>
+    <t>1000 OR
+840 EXP
+4 PARCHEMINS
+4 EQUIP</t>
   </si>
   <si>
     <t>COULOIRS INFERNAUX</t>
@@ -290,7 +315,10 @@
     <t>47,42,11</t>
   </si>
   <si>
-    <t>1200 EXP + 1200 PO + 12 PARCHEMIN</t>
+    <t>2400 OR
+1000 EXP
+5 PARCHEMINS
+4 EQUIP</t>
   </si>
   <si>
     <t>FORTERESSE DU SEIGNEUR DES ENFERS</t>
@@ -314,69 +342,49 @@
     <t>45,40,15</t>
   </si>
   <si>
-    <t>1500 EXP + 1500 PO + 15 PARCHEMIN</t>
+    <t>3000 OR
+1500 EX
+10 PARCHEMINS
+5 EQUIP
+10 TOME D’EXP **</t>
   </si>
   <si>
     <t>3-4</t>
   </si>
   <si>
-    <t>2100 EXP + 2100 PO + 21 PARCHEMIN</t>
-  </si>
-  <si>
     <t>35</t>
   </si>
   <si>
-    <t>2450 EXP + 2450 PO + 25 PARCHEMIN</t>
-  </si>
-  <si>
     <t>CAVERNE HUMIDE</t>
   </si>
   <si>
     <t>41</t>
   </si>
   <si>
-    <t>2870 EXP + 2870 PO + 29 PARCHEMIN</t>
-  </si>
-  <si>
     <t>48</t>
   </si>
   <si>
-    <t>3360 EXP + 3360 PO + 34 PARCHEMIN</t>
-  </si>
-  <si>
     <t>56</t>
   </si>
   <si>
     <t>4-5</t>
   </si>
   <si>
-    <t>3920 EXP + 3920 PO + 39 PARCHEMIN</t>
-  </si>
-  <si>
     <t>64</t>
   </si>
   <si>
-    <t>4480 EXP + 4480 PO + 45 PARCHEMIN</t>
-  </si>
-  <si>
     <t>72</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>5040 EXP + 5040 PO + 50 PARCHEMIN</t>
-  </si>
-  <si>
     <t>81</t>
   </si>
   <si>
     <t>40,40,20</t>
   </si>
   <si>
-    <t>5670 EXP + 5670 PO + 57 PARCHEMIN</t>
-  </si>
-  <si>
     <t>90</t>
   </si>
   <si>
@@ -386,88 +394,52 @@
     <t>39,39,22</t>
   </si>
   <si>
-    <t>6300 EXP + 6300 PO + 63 PARCHEMIN</t>
-  </si>
-  <si>
     <t>37,38,25</t>
   </si>
   <si>
-    <t>7000 EXP + 7000 PO + 70 PARCHEMIN</t>
-  </si>
-  <si>
     <t>200</t>
   </si>
   <si>
-    <t>8000 EXP + 8000 PO + 80 PARCHEMIN</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
-    <t>9200 EXP + 9200 PO + 92 PARCHEMIN</t>
-  </si>
-  <si>
     <t>260</t>
   </si>
   <si>
     <t>6-7</t>
   </si>
   <si>
-    <t>10400 EXP + 10400 PO + 104 PARCHEMIN</t>
-  </si>
-  <si>
     <t>300</t>
   </si>
   <si>
-    <t>12000 EXP + 12000 PO + 120 PARCHEMIN</t>
-  </si>
-  <si>
     <t>350</t>
   </si>
   <si>
-    <t>14000 EXP + 14000 PO + 140 PARCHEMIN</t>
-  </si>
-  <si>
     <t>400</t>
   </si>
   <si>
-    <t>16000 EXP + 16000 PO + 160 PARCHEMIN</t>
-  </si>
-  <si>
     <t>450</t>
   </si>
   <si>
     <t>7-8</t>
   </si>
   <si>
-    <t>18000 EXP + 18000 PO + 180 PARCHEMIN</t>
-  </si>
-  <si>
     <t>500</t>
   </si>
   <si>
     <t>34,35,29,2</t>
   </si>
   <si>
-    <t>20000 EXP + 20000 PO + 200 PARCHEMIN</t>
-  </si>
-  <si>
     <t>550</t>
   </si>
   <si>
     <t>33,34,30,3</t>
   </si>
   <si>
-    <t>22000 EXP + 22000 PO + 220 PARCHEMIN</t>
-  </si>
-  <si>
     <t>600</t>
   </si>
   <si>
     <t>31,31,33,5</t>
-  </si>
-  <si>
-    <t>24000 EXP + 24000 PO + 240 PARCHEMIN</t>
   </si>
   <si>
     <t>PINNACLE DU MAL ABSOLU (niveau caché, apparait uniquement quand le 3-10 est vaincu)</t>
@@ -498,7 +470,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -510,15 +482,14 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="10"/>
+      <sz val="15"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="10"/>
-      <color indexed="12"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
@@ -530,17 +501,23 @@
     <font>
       <b val="1"/>
       <sz val="10"/>
-      <color indexed="15"/>
+      <color indexed="16"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="10"/>
-      <color indexed="16"/>
+      <color indexed="17"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+      <color indexed="18"/>
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -555,12 +532,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="13"/>
+        <fgColor indexed="12"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="15"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -572,6 +555,28 @@
       <left style="thin">
         <color indexed="10"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="10"/>
       </right>
@@ -585,7 +590,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
         <color indexed="11"/>
@@ -594,7 +599,7 @@
         <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,43 +608,28 @@
         <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
         <color indexed="11"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,28 +638,58 @@
         <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
       </bottom>
       <diagonal/>
     </border>
@@ -679,53 +699,59 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -745,8 +771,10 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ffbdc0bf"/>
-      <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff3f3f3f"/>
       <rgbColor rgb="ff017000"/>
       <rgbColor rgb="ffdbdbdb"/>
@@ -769,10 +797,10 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="5E5E5E"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="D5D5D5"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="00A2FF"/>
@@ -949,11 +977,14 @@
     <a:spDef>
       <a:spPr>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:miter lim="400000"/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -962,7 +993,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="584200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -976,19 +1007,19 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
             <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Helvetica Neue Medium"/>
-            <a:ea typeface="Helvetica Neue Medium"/>
-            <a:cs typeface="Helvetica Neue Medium"/>
-            <a:sym typeface="Helvetica Neue Medium"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1227,12 +1258,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
-            <a:srgbClr val="000000"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="400000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1513,7 +1544,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="457200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1781,22 +1812,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:M94"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="24.5469" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.2656" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.07812" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.6562" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.2891" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.7734" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.9062" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3516" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.17188" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.6719" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.3516" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.8516" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5781" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.2812" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="28.2812" style="1" customWidth="1"/>
-    <col min="13" max="13" width="35.6016" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6719" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.3516" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.3516" style="1" customWidth="1"/>
+    <col min="12" max="12" width="28.3516" style="1" customWidth="1"/>
+    <col min="13" max="13" width="35.6719" style="1" customWidth="1"/>
     <col min="14" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1804,2271 +1835,2201 @@
       <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" ht="32.25" customHeight="1">
-      <c r="A2" t="s" s="3">
+      <c r="A2" t="s" s="5">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="3">
+      <c r="B2" t="s" s="5">
         <v>2</v>
       </c>
-      <c r="C2" t="s" s="3">
+      <c r="C2" t="s" s="5">
         <v>3</v>
       </c>
-      <c r="D2" t="s" s="3">
+      <c r="D2" t="s" s="5">
         <v>4</v>
       </c>
-      <c r="E2" t="s" s="3">
+      <c r="E2" t="s" s="5">
         <v>5</v>
       </c>
-      <c r="F2" t="s" s="3">
+      <c r="F2" t="s" s="5">
         <v>6</v>
       </c>
-      <c r="G2" t="s" s="3">
+      <c r="G2" t="s" s="5">
         <v>7</v>
       </c>
-      <c r="H2" t="s" s="3">
+      <c r="H2" t="s" s="5">
         <v>8</v>
       </c>
-      <c r="I2" t="s" s="3">
+      <c r="I2" t="s" s="5">
         <v>9</v>
       </c>
-      <c r="J2" t="s" s="3">
+      <c r="J2" t="s" s="5">
         <v>10</v>
       </c>
-      <c r="K2" t="s" s="3">
+      <c r="K2" t="s" s="5">
         <v>11</v>
       </c>
-      <c r="L2" t="s" s="3">
+      <c r="L2" t="s" s="5">
         <v>12</v>
       </c>
-      <c r="M2" t="s" s="3">
+      <c r="M2" t="s" s="5">
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="32.25" customHeight="1">
-      <c r="A3" t="s" s="4">
+    <row r="3" ht="57.85" customHeight="1">
+      <c r="A3" t="s" s="6">
         <v>14</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" t="s" s="6">
+      <c r="C3" t="s" s="8">
         <v>15</v>
       </c>
-      <c r="D3" t="s" s="6">
+      <c r="D3" t="s" s="8">
         <v>16</v>
       </c>
-      <c r="E3" t="s" s="6">
+      <c r="E3" t="s" s="8">
         <v>17</v>
       </c>
-      <c r="F3" t="s" s="6">
+      <c r="F3" t="s" s="8">
         <v>18</v>
       </c>
-      <c r="G3" t="s" s="6">
+      <c r="G3" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="H3" t="s" s="6">
+      <c r="H3" t="s" s="8">
         <v>20</v>
       </c>
-      <c r="I3" t="s" s="6">
+      <c r="I3" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="J3" s="7" cm="1">
+      <c r="J3" s="9" cm="1">
         <f t="array" ref="J3">100*B3</f>
         <v>100</v>
       </c>
-      <c r="K3" s="7" cm="1">
+      <c r="K3" s="9" cm="1">
         <f t="array" ref="K3">ROUND(40*(B3*0.7),0)</f>
         <v>28</v>
       </c>
-      <c r="L3" t="str" s="6" cm="1">
-        <f t="array" ref="L3">ROUND(B3*100*1,0)&amp;" EXP + "&amp;ROUND(B3*100*1,0)&amp;" PO + "&amp;ROUND(B3*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>100 EXP + 100 PO + 1 PARCHEMIN</v>
-      </c>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" ht="32.05" customHeight="1">
-      <c r="A4" t="s" s="8">
+      <c r="L3" t="s" s="8">
+        <v>21</v>
+      </c>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" ht="57.5" customHeight="1">
+      <c r="A4" t="s" s="10">
         <v>22</v>
       </c>
-      <c r="B4" t="s" s="9">
+      <c r="B4" t="s" s="11">
         <v>23</v>
       </c>
-      <c r="C4" t="s" s="10">
+      <c r="C4" t="s" s="12">
         <v>24</v>
       </c>
-      <c r="D4" t="s" s="10">
+      <c r="D4" t="s" s="12">
         <v>25</v>
       </c>
-      <c r="E4" t="s" s="10">
+      <c r="E4" t="s" s="12">
         <v>26</v>
       </c>
-      <c r="F4" t="s" s="10">
+      <c r="F4" t="s" s="12">
         <v>27</v>
       </c>
-      <c r="G4" t="s" s="10">
+      <c r="G4" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="H4" t="s" s="10">
+      <c r="H4" t="s" s="12">
         <v>28</v>
       </c>
-      <c r="I4" t="s" s="10">
+      <c r="I4" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J4" s="11" cm="1">
+      <c r="J4" s="13" cm="1">
         <f t="array" ref="J4">100*B4</f>
         <v>150</v>
       </c>
-      <c r="K4" s="11" cm="1">
+      <c r="K4" s="13" cm="1">
         <f t="array" ref="K4">ROUND(40*(B4*0.7),0)</f>
         <v>42</v>
       </c>
-      <c r="L4" t="str" s="10" cm="1">
-        <f t="array" ref="L4">ROUND(B4*100*1,0)&amp;" EXP + "&amp;ROUND(B4*100*1,0)&amp;" PO + "&amp;ROUND(B4*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>150 EXP + 150 PO + 2 PARCHEMIN</v>
-      </c>
-      <c r="M4" s="10"/>
-    </row>
-    <row r="5" ht="32.05" customHeight="1">
-      <c r="A5" t="s" s="8">
+      <c r="L4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" ht="57.5" customHeight="1">
+      <c r="A5" t="s" s="10">
         <v>30</v>
       </c>
-      <c r="B5" t="s" s="9">
+      <c r="B5" t="s" s="11">
         <v>31</v>
       </c>
-      <c r="C5" t="s" s="10">
+      <c r="C5" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="D5" t="s" s="10">
+      <c r="D5" t="s" s="12">
         <v>33</v>
       </c>
-      <c r="E5" t="s" s="10">
+      <c r="E5" t="s" s="12">
         <v>34</v>
       </c>
-      <c r="F5" t="s" s="10">
+      <c r="F5" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="G5" t="s" s="10">
+      <c r="G5" t="s" s="12">
         <v>36</v>
       </c>
-      <c r="H5" t="s" s="10">
+      <c r="H5" t="s" s="12">
         <v>37</v>
       </c>
-      <c r="I5" t="s" s="10">
+      <c r="I5" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J5" s="11" cm="1">
+      <c r="J5" s="13" cm="1">
         <f t="array" ref="J5">100*B5</f>
         <v>210</v>
       </c>
-      <c r="K5" s="11" cm="1">
+      <c r="K5" s="13" cm="1">
         <f t="array" ref="K5">ROUND(40*(B5*0.7),0)</f>
         <v>59</v>
       </c>
-      <c r="L5" t="str" s="10" cm="1">
-        <f t="array" ref="L5">ROUND(B5*100*1,0)&amp;" EXP + "&amp;ROUND(B5*100*1,0)&amp;" PO + "&amp;ROUND(B5*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>210 EXP + 210 PO + 2 PARCHEMIN</v>
-      </c>
-      <c r="M5" s="10"/>
-    </row>
-    <row r="6" ht="32.05" customHeight="1">
-      <c r="A6" t="s" s="8">
+      <c r="L5" t="s" s="12">
+        <v>38</v>
+      </c>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" ht="57.5" customHeight="1">
+      <c r="A6" t="s" s="10">
         <v>39</v>
       </c>
-      <c r="B6" t="s" s="9">
+      <c r="B6" t="s" s="11">
         <v>40</v>
       </c>
-      <c r="C6" t="s" s="10">
+      <c r="C6" t="s" s="12">
         <v>41</v>
       </c>
-      <c r="D6" t="s" s="10">
+      <c r="D6" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="E6" t="s" s="10">
+      <c r="E6" t="s" s="12">
         <v>43</v>
       </c>
-      <c r="F6" t="s" s="10">
+      <c r="F6" t="s" s="12">
         <v>44</v>
       </c>
-      <c r="G6" t="s" s="10">
+      <c r="G6" t="s" s="12">
         <v>36</v>
       </c>
-      <c r="H6" t="s" s="10">
+      <c r="H6" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="I6" t="s" s="10">
+      <c r="I6" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J6" s="11" cm="1">
+      <c r="J6" s="13" cm="1">
         <f t="array" ref="J6">100*B6</f>
         <v>300</v>
       </c>
-      <c r="K6" s="11" cm="1">
+      <c r="K6" s="13" cm="1">
         <f t="array" ref="K6">ROUND(40*(B6*0.7),0)</f>
         <v>84</v>
       </c>
-      <c r="L6" t="str" s="10" cm="1">
-        <f t="array" ref="L6">ROUND(B6*100*1,0)&amp;" EXP + "&amp;ROUND(B6*100*1,0)&amp;" PO + "&amp;ROUND(B6*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>300 EXP + 300 PO + 3 PARCHEMIN</v>
-      </c>
-      <c r="M6" s="10"/>
-    </row>
-    <row r="7" ht="32.05" customHeight="1">
-      <c r="A7" t="s" s="8">
+      <c r="L6" t="s" s="12">
+        <v>46</v>
+      </c>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" ht="57.5" customHeight="1">
+      <c r="A7" t="s" s="10">
         <v>47</v>
       </c>
-      <c r="B7" t="s" s="9">
+      <c r="B7" t="s" s="11">
         <v>48</v>
       </c>
-      <c r="C7" t="s" s="10">
+      <c r="C7" t="s" s="12">
         <v>49</v>
       </c>
-      <c r="D7" t="s" s="10">
+      <c r="D7" t="s" s="12">
         <v>50</v>
       </c>
-      <c r="E7" t="s" s="10">
+      <c r="E7" t="s" s="12">
         <v>51</v>
       </c>
-      <c r="F7" t="s" s="10">
+      <c r="F7" t="s" s="12">
         <v>52</v>
       </c>
-      <c r="G7" t="s" s="10">
+      <c r="G7" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="H7" t="s" s="10">
+      <c r="H7" t="s" s="12">
         <v>54</v>
       </c>
-      <c r="I7" t="s" s="10">
+      <c r="I7" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J7" s="11" cm="1">
+      <c r="J7" s="13" cm="1">
         <f t="array" ref="J7">100*B7</f>
         <v>400</v>
       </c>
-      <c r="K7" s="11" cm="1">
+      <c r="K7" s="13" cm="1">
         <f t="array" ref="K7">ROUND(40*(B7*0.7),0)</f>
         <v>112</v>
       </c>
-      <c r="L7" t="str" s="10" cm="1">
-        <f t="array" ref="L7">ROUND(B7*100*1,0)&amp;" EXP + "&amp;ROUND(B7*100*1,0)&amp;" PO + "&amp;ROUND(B7*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>400 EXP + 400 PO + 4 PARCHEMIN</v>
-      </c>
-      <c r="M7" s="10"/>
-    </row>
-    <row r="8" ht="32.05" customHeight="1">
-      <c r="A8" t="s" s="8">
+      <c r="L7" t="s" s="12">
+        <v>55</v>
+      </c>
+      <c r="M7" s="12"/>
+    </row>
+    <row r="8" ht="57.5" customHeight="1">
+      <c r="A8" t="s" s="10">
         <v>56</v>
       </c>
-      <c r="B8" t="s" s="9">
+      <c r="B8" t="s" s="11">
         <v>57</v>
       </c>
-      <c r="C8" t="s" s="10">
+      <c r="C8" t="s" s="12">
         <v>58</v>
       </c>
-      <c r="D8" t="s" s="10">
+      <c r="D8" t="s" s="12">
         <v>59</v>
       </c>
-      <c r="E8" t="s" s="10">
+      <c r="E8" t="s" s="12">
         <v>60</v>
       </c>
-      <c r="F8" t="s" s="10">
+      <c r="F8" t="s" s="12">
         <v>61</v>
       </c>
-      <c r="G8" t="s" s="10">
+      <c r="G8" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="H8" t="s" s="10">
+      <c r="H8" t="s" s="12">
         <v>62</v>
       </c>
-      <c r="I8" t="s" s="10">
+      <c r="I8" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J8" s="11" cm="1">
+      <c r="J8" s="13" cm="1">
         <f t="array" ref="J8">100*B8</f>
         <v>550</v>
       </c>
-      <c r="K8" s="11" cm="1">
+      <c r="K8" s="13" cm="1">
         <f t="array" ref="K8">ROUND(40*(B8*0.7),0)</f>
         <v>154</v>
       </c>
-      <c r="L8" t="str" s="10" cm="1">
-        <f t="array" ref="L8">ROUND(B8*100*1,0)&amp;" EXP + "&amp;ROUND(B8*100*1,0)&amp;" PO + "&amp;ROUND(B8*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>550 EXP + 550 PO + 6 PARCHEMIN</v>
-      </c>
-      <c r="M8" s="10"/>
-    </row>
-    <row r="9" ht="32.05" customHeight="1">
-      <c r="A9" t="s" s="8">
+      <c r="L8" t="s" s="12">
+        <v>63</v>
+      </c>
+      <c r="M8" s="12"/>
+    </row>
+    <row r="9" ht="57.5" customHeight="1">
+      <c r="A9" t="s" s="10">
         <v>64</v>
       </c>
-      <c r="B9" t="s" s="9">
+      <c r="B9" t="s" s="11">
         <v>32</v>
       </c>
-      <c r="C9" t="s" s="10">
+      <c r="C9" t="s" s="12">
         <v>65</v>
       </c>
-      <c r="D9" t="s" s="10">
+      <c r="D9" t="s" s="12">
         <v>66</v>
       </c>
-      <c r="E9" t="s" s="10">
+      <c r="E9" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="F9" t="s" s="10">
+      <c r="F9" t="s" s="12">
         <v>68</v>
       </c>
-      <c r="G9" t="s" s="10">
+      <c r="G9" t="s" s="12">
         <v>69</v>
       </c>
-      <c r="H9" t="s" s="10">
+      <c r="H9" t="s" s="12">
         <v>70</v>
       </c>
-      <c r="I9" t="s" s="10">
+      <c r="I9" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J9" s="11" cm="1">
+      <c r="J9" s="13" cm="1">
         <f t="array" ref="J9">100*B9</f>
         <v>800</v>
       </c>
-      <c r="K9" s="11" cm="1">
+      <c r="K9" s="13" cm="1">
         <f t="array" ref="K9">ROUND(40*(B9*0.7),0)</f>
         <v>224</v>
       </c>
-      <c r="L9" t="str" s="10" cm="1">
-        <f t="array" ref="L9">ROUND(B9*100*1,0)&amp;" EXP + "&amp;ROUND(B9*100*1,0)&amp;" PO + "&amp;ROUND(B9*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>800 EXP + 800 PO + 8 PARCHEMIN</v>
-      </c>
-      <c r="M9" s="10"/>
-    </row>
-    <row r="10" ht="44.05" customHeight="1">
-      <c r="A10" t="s" s="8">
+      <c r="L9" t="s" s="12">
+        <v>71</v>
+      </c>
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" ht="79" customHeight="1">
+      <c r="A10" t="s" s="10">
         <v>72</v>
       </c>
-      <c r="B10" t="s" s="9">
+      <c r="B10" t="s" s="11">
         <v>41</v>
       </c>
-      <c r="C10" t="s" s="10">
+      <c r="C10" t="s" s="12">
         <v>73</v>
       </c>
-      <c r="D10" t="s" s="10">
+      <c r="D10" t="s" s="12">
         <v>74</v>
       </c>
-      <c r="E10" t="s" s="10">
+      <c r="E10" t="s" s="12">
         <v>75</v>
       </c>
-      <c r="F10" t="s" s="10">
+      <c r="F10" t="s" s="12">
         <v>76</v>
       </c>
-      <c r="G10" t="s" s="10">
+      <c r="G10" t="s" s="12">
         <v>69</v>
       </c>
-      <c r="H10" t="s" s="10">
+      <c r="H10" t="s" s="12">
         <v>77</v>
       </c>
-      <c r="I10" t="s" s="10">
+      <c r="I10" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="J10" s="11" cm="1">
+      <c r="J10" s="13" cm="1">
         <f t="array" ref="J10">100*B10</f>
         <v>1000</v>
       </c>
-      <c r="K10" s="11" cm="1">
+      <c r="K10" s="13" cm="1">
         <f t="array" ref="K10">ROUND(40*(B10*0.7),0)</f>
         <v>280</v>
       </c>
-      <c r="L10" t="str" s="10" cm="1">
-        <f t="array" ref="L10">ROUND(B10*100*1,0)&amp;" EXP + "&amp;ROUND(B10*100*1,0)&amp;" PO + "&amp;ROUND(B10*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>1000 EXP + 1000 PO + 10 PARCHEMIN</v>
-      </c>
-      <c r="M10" s="10"/>
-    </row>
-    <row r="11" ht="44.05" customHeight="1">
-      <c r="A11" t="s" s="8">
+      <c r="L10" t="s" s="12">
+        <v>78</v>
+      </c>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" ht="100.8" customHeight="1">
+      <c r="A11" t="s" s="10">
         <v>79</v>
       </c>
-      <c r="B11" t="s" s="9">
+      <c r="B11" t="s" s="11">
         <v>49</v>
       </c>
-      <c r="C11" t="s" s="10">
+      <c r="C11" t="s" s="12">
         <v>80</v>
       </c>
-      <c r="D11" t="s" s="10">
+      <c r="D11" t="s" s="12">
         <v>81</v>
       </c>
-      <c r="E11" t="s" s="10">
+      <c r="E11" t="s" s="12">
         <v>82</v>
       </c>
-      <c r="F11" t="s" s="10">
+      <c r="F11" t="s" s="12">
         <v>83</v>
       </c>
-      <c r="G11" t="s" s="10">
+      <c r="G11" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="H11" t="s" s="10">
+      <c r="H11" t="s" s="12">
         <v>84</v>
       </c>
-      <c r="I11" t="s" s="10">
+      <c r="I11" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="J11" s="11" cm="1">
+      <c r="J11" s="13" cm="1">
         <f t="array" ref="J11">100*B11</f>
         <v>1200</v>
       </c>
-      <c r="K11" s="11" cm="1">
+      <c r="K11" s="13" cm="1">
         <f t="array" ref="K11">ROUND(40*(B11*0.7),0)</f>
         <v>336</v>
       </c>
-      <c r="L11" t="str" s="10" cm="1">
-        <f t="array" ref="L11">ROUND(B11*100*1,0)&amp;" EXP + "&amp;ROUND(B11*100*1,0)&amp;" PO + "&amp;ROUND(B11*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>1200 EXP + 1200 PO + 12 PARCHEMIN</v>
-      </c>
-      <c r="M11" s="10"/>
-    </row>
-    <row r="12" ht="44.05" customHeight="1">
-      <c r="A12" t="s" s="8">
+      <c r="L11" t="s" s="12">
+        <v>85</v>
+      </c>
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" ht="100.2" customHeight="1">
+      <c r="A12" t="s" s="10">
         <v>86</v>
       </c>
-      <c r="B12" t="s" s="9">
+      <c r="B12" t="s" s="11">
         <v>87</v>
       </c>
-      <c r="C12" t="s" s="10">
+      <c r="C12" t="s" s="12">
         <v>88</v>
       </c>
-      <c r="D12" t="s" s="10">
+      <c r="D12" t="s" s="12">
         <v>89</v>
       </c>
-      <c r="E12" t="s" s="10">
+      <c r="E12" t="s" s="12">
         <v>90</v>
       </c>
-      <c r="F12" t="s" s="10">
+      <c r="F12" t="s" s="12">
         <v>91</v>
       </c>
-      <c r="G12" t="s" s="10">
+      <c r="G12" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="H12" t="s" s="10">
+      <c r="H12" t="s" s="12">
         <v>92</v>
       </c>
-      <c r="I12" t="s" s="10">
+      <c r="I12" t="s" s="12">
         <v>48</v>
       </c>
-      <c r="J12" s="11" cm="1">
+      <c r="J12" s="13" cm="1">
         <f t="array" ref="J12">100*B12</f>
         <v>1500</v>
       </c>
-      <c r="K12" s="11" cm="1">
+      <c r="K12" s="13" cm="1">
         <f t="array" ref="K12">ROUND(40*(B12*0.7),0)</f>
         <v>420</v>
       </c>
-      <c r="L12" t="str" s="10" cm="1">
-        <f t="array" ref="L12">ROUND(B12*100*1,0)&amp;" EXP + "&amp;ROUND(B12*100*1,0)&amp;" PO + "&amp;ROUND(B12*1*1,0)&amp;" PARCHEMIN"</f>
-        <v>1500 EXP + 1500 PO + 15 PARCHEMIN</v>
-      </c>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" ht="32.05" customHeight="1">
-      <c r="A13" t="s" s="12">
+      <c r="L12" t="s" s="12">
+        <v>93</v>
+      </c>
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" ht="57.5" customHeight="1">
+      <c r="A13" t="s" s="14">
         <v>14</v>
       </c>
-      <c r="B13" t="s" s="9">
+      <c r="B13" t="s" s="11">
         <v>88</v>
       </c>
-      <c r="C13" t="s" s="10">
+      <c r="C13" t="s" s="12">
         <v>15</v>
       </c>
-      <c r="D13" t="s" s="10">
+      <c r="D13" t="s" s="12">
         <v>16</v>
       </c>
-      <c r="E13" t="s" s="10">
+      <c r="E13" t="s" s="12">
         <v>17</v>
       </c>
-      <c r="F13" t="s" s="10">
+      <c r="F13" t="s" s="12">
         <v>18</v>
       </c>
-      <c r="G13" t="s" s="10">
+      <c r="G13" t="s" s="12">
         <v>94</v>
       </c>
-      <c r="H13" t="s" s="10">
+      <c r="H13" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="I13" t="s" s="10">
+      <c r="I13" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J13" s="11" cm="1">
+      <c r="J13" s="13" cm="1">
         <f t="array" ref="J13">100*B13</f>
         <v>3000</v>
       </c>
-      <c r="K13" s="11" cm="1">
+      <c r="K13" s="13" cm="1">
         <f t="array" ref="K13">ROUND(40*(B13*0.5),0)</f>
         <v>600</v>
       </c>
-      <c r="L13" t="str" s="10" cm="1">
-        <f t="array" ref="L13">ROUND(B13*100*0.7,0)&amp;" EXP + "&amp;ROUND(B13*100*0.7,0)&amp;" PO + "&amp;ROUND(B13*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>2100 EXP + 2100 PO + 21 PARCHEMIN</v>
-      </c>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" ht="32.05" customHeight="1">
-      <c r="A14" t="s" s="12">
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" ht="57.5" customHeight="1">
+      <c r="A14" t="s" s="14">
         <v>22</v>
       </c>
-      <c r="B14" t="s" s="9">
-        <v>96</v>
-      </c>
-      <c r="C14" t="s" s="10">
+      <c r="B14" t="s" s="11">
+        <v>95</v>
+      </c>
+      <c r="C14" t="s" s="12">
         <v>24</v>
       </c>
-      <c r="D14" t="s" s="10">
+      <c r="D14" t="s" s="12">
         <v>25</v>
       </c>
-      <c r="E14" t="s" s="10">
+      <c r="E14" t="s" s="12">
         <v>26</v>
       </c>
-      <c r="F14" t="s" s="10">
+      <c r="F14" t="s" s="12">
         <v>27</v>
       </c>
-      <c r="G14" t="s" s="10">
+      <c r="G14" t="s" s="12">
         <v>94</v>
       </c>
-      <c r="H14" t="s" s="10">
+      <c r="H14" t="s" s="12">
         <v>54</v>
       </c>
-      <c r="I14" t="s" s="10">
+      <c r="I14" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J14" s="11" cm="1">
+      <c r="J14" s="13" cm="1">
         <f t="array" ref="J14">100*B14</f>
         <v>3500</v>
       </c>
-      <c r="K14" s="11" cm="1">
+      <c r="K14" s="13" cm="1">
         <f t="array" ref="K14">ROUND(40*(B14*0.5),0)</f>
         <v>700</v>
       </c>
-      <c r="L14" t="str" s="10" cm="1">
-        <f t="array" ref="L14">ROUND(B14*100*0.7,0)&amp;" EXP + "&amp;ROUND(B14*100*0.7,0)&amp;" PO + "&amp;ROUND(B14*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>2450 EXP + 2450 PO + 25 PARCHEMIN</v>
-      </c>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" ht="32.05" customHeight="1">
-      <c r="A15" t="s" s="12">
-        <v>98</v>
-      </c>
-      <c r="B15" t="s" s="9">
-        <v>99</v>
-      </c>
-      <c r="C15" t="s" s="10">
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" ht="57.5" customHeight="1">
+      <c r="A15" t="s" s="14">
+        <v>96</v>
+      </c>
+      <c r="B15" t="s" s="11">
+        <v>97</v>
+      </c>
+      <c r="C15" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="D15" t="s" s="10">
+      <c r="D15" t="s" s="12">
         <v>33</v>
       </c>
-      <c r="E15" t="s" s="10">
+      <c r="E15" t="s" s="12">
         <v>34</v>
       </c>
-      <c r="F15" t="s" s="10">
+      <c r="F15" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="G15" t="s" s="10">
+      <c r="G15" t="s" s="12">
         <v>48</v>
       </c>
-      <c r="H15" t="s" s="10">
+      <c r="H15" t="s" s="12">
         <v>62</v>
       </c>
-      <c r="I15" t="s" s="10">
+      <c r="I15" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J15" s="11" cm="1">
+      <c r="J15" s="13" cm="1">
         <f t="array" ref="J15">100*B15</f>
         <v>4100</v>
       </c>
-      <c r="K15" s="11" cm="1">
+      <c r="K15" s="13" cm="1">
         <f t="array" ref="K15">ROUND(40*(B15*0.5),0)</f>
         <v>820</v>
       </c>
-      <c r="L15" t="str" s="10" cm="1">
-        <f t="array" ref="L15">ROUND(B15*100*0.7,0)&amp;" EXP + "&amp;ROUND(B15*100*0.7,0)&amp;" PO + "&amp;ROUND(B15*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>2870 EXP + 2870 PO + 29 PARCHEMIN</v>
-      </c>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" ht="32.05" customHeight="1">
-      <c r="A16" t="s" s="12">
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" ht="57.5" customHeight="1">
+      <c r="A16" t="s" s="14">
         <v>39</v>
       </c>
-      <c r="B16" t="s" s="9">
-        <v>101</v>
-      </c>
-      <c r="C16" t="s" s="10">
+      <c r="B16" t="s" s="11">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s" s="12">
         <v>41</v>
       </c>
-      <c r="D16" t="s" s="10">
+      <c r="D16" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="E16" t="s" s="10">
+      <c r="E16" t="s" s="12">
         <v>43</v>
       </c>
-      <c r="F16" t="s" s="10">
+      <c r="F16" t="s" s="12">
         <v>44</v>
       </c>
-      <c r="G16" t="s" s="10">
+      <c r="G16" t="s" s="12">
         <v>48</v>
       </c>
-      <c r="H16" t="s" s="10">
+      <c r="H16" t="s" s="12">
         <v>70</v>
       </c>
-      <c r="I16" t="s" s="10">
+      <c r="I16" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J16" s="11" cm="1">
+      <c r="J16" s="13" cm="1">
         <f t="array" ref="J16">100*B16</f>
         <v>4800</v>
       </c>
-      <c r="K16" s="11" cm="1">
+      <c r="K16" s="13" cm="1">
         <f t="array" ref="K16">ROUND(40*(B16*0.5),0)</f>
         <v>960</v>
       </c>
-      <c r="L16" t="str" s="10" cm="1">
-        <f t="array" ref="L16">ROUND(B16*100*0.7,0)&amp;" EXP + "&amp;ROUND(B16*100*0.7,0)&amp;" PO + "&amp;ROUND(B16*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>3360 EXP + 3360 PO + 34 PARCHEMIN</v>
-      </c>
-      <c r="M16" s="10"/>
-    </row>
-    <row r="17" ht="32.05" customHeight="1">
-      <c r="A17" t="s" s="12">
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" ht="57.5" customHeight="1">
+      <c r="A17" t="s" s="14">
         <v>47</v>
       </c>
-      <c r="B17" t="s" s="9">
-        <v>103</v>
-      </c>
-      <c r="C17" t="s" s="10">
+      <c r="B17" t="s" s="11">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s" s="12">
         <v>49</v>
       </c>
-      <c r="D17" t="s" s="10">
+      <c r="D17" t="s" s="12">
         <v>50</v>
       </c>
-      <c r="E17" t="s" s="10">
+      <c r="E17" t="s" s="12">
         <v>51</v>
       </c>
-      <c r="F17" t="s" s="10">
+      <c r="F17" t="s" s="12">
         <v>52</v>
       </c>
-      <c r="G17" t="s" s="10">
-        <v>104</v>
-      </c>
-      <c r="H17" t="s" s="10">
+      <c r="G17" t="s" s="12">
+        <v>100</v>
+      </c>
+      <c r="H17" t="s" s="12">
         <v>77</v>
       </c>
-      <c r="I17" t="s" s="10">
+      <c r="I17" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J17" s="11" cm="1">
+      <c r="J17" s="13" cm="1">
         <f t="array" ref="J17">100*B17</f>
         <v>5600</v>
       </c>
-      <c r="K17" s="11" cm="1">
+      <c r="K17" s="13" cm="1">
         <f t="array" ref="K17">ROUND(40*(B17*0.5),0)</f>
         <v>1120</v>
       </c>
-      <c r="L17" t="str" s="10" cm="1">
-        <f t="array" ref="L17">ROUND(B17*100*0.7,0)&amp;" EXP + "&amp;ROUND(B17*100*0.7,0)&amp;" PO + "&amp;ROUND(B17*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>3920 EXP + 3920 PO + 39 PARCHEMIN</v>
-      </c>
-      <c r="M17" s="10"/>
-    </row>
-    <row r="18" ht="32.05" customHeight="1">
-      <c r="A18" t="s" s="12">
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" ht="57.5" customHeight="1">
+      <c r="A18" t="s" s="14">
         <v>56</v>
       </c>
-      <c r="B18" t="s" s="9">
-        <v>106</v>
-      </c>
-      <c r="C18" t="s" s="10">
+      <c r="B18" t="s" s="11">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s" s="12">
         <v>58</v>
       </c>
-      <c r="D18" t="s" s="10">
+      <c r="D18" t="s" s="12">
         <v>59</v>
       </c>
-      <c r="E18" t="s" s="10">
+      <c r="E18" t="s" s="12">
         <v>60</v>
       </c>
-      <c r="F18" t="s" s="10">
+      <c r="F18" t="s" s="12">
         <v>61</v>
       </c>
-      <c r="G18" t="s" s="10">
-        <v>104</v>
-      </c>
-      <c r="H18" t="s" s="10">
+      <c r="G18" t="s" s="12">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s" s="12">
         <v>84</v>
       </c>
-      <c r="I18" t="s" s="10">
+      <c r="I18" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J18" s="11" cm="1">
+      <c r="J18" s="13" cm="1">
         <f t="array" ref="J18">100*B18</f>
         <v>6400</v>
       </c>
-      <c r="K18" s="11" cm="1">
+      <c r="K18" s="13" cm="1">
         <f t="array" ref="K18">ROUND(40*(B18*0.5),0)</f>
         <v>1280</v>
       </c>
-      <c r="L18" t="str" s="10" cm="1">
-        <f t="array" ref="L18">ROUND(B18*100*0.7,0)&amp;" EXP + "&amp;ROUND(B18*100*0.7,0)&amp;" PO + "&amp;ROUND(B18*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>4480 EXP + 4480 PO + 45 PARCHEMIN</v>
-      </c>
-      <c r="M18" s="10"/>
-    </row>
-    <row r="19" ht="32.05" customHeight="1">
-      <c r="A19" t="s" s="12">
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" ht="57.5" customHeight="1">
+      <c r="A19" t="s" s="14">
         <v>64</v>
       </c>
-      <c r="B19" t="s" s="9">
-        <v>108</v>
-      </c>
-      <c r="C19" t="s" s="10">
+      <c r="B19" t="s" s="11">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s" s="12">
         <v>65</v>
       </c>
-      <c r="D19" t="s" s="10">
+      <c r="D19" t="s" s="12">
         <v>66</v>
       </c>
-      <c r="E19" t="s" s="10">
+      <c r="E19" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="F19" t="s" s="10">
+      <c r="F19" t="s" s="12">
         <v>68</v>
       </c>
-      <c r="G19" t="s" s="10">
-        <v>109</v>
-      </c>
-      <c r="H19" t="s" s="10">
+      <c r="G19" t="s" s="12">
+        <v>103</v>
+      </c>
+      <c r="H19" t="s" s="12">
         <v>92</v>
       </c>
-      <c r="I19" t="s" s="10">
+      <c r="I19" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J19" s="11" cm="1">
+      <c r="J19" s="13" cm="1">
         <f t="array" ref="J19">100*B19</f>
         <v>7200</v>
       </c>
-      <c r="K19" s="11" cm="1">
+      <c r="K19" s="13" cm="1">
         <f t="array" ref="K19">ROUND(40*(B19*0.5),0)</f>
         <v>1440</v>
       </c>
-      <c r="L19" t="str" s="10" cm="1">
-        <f t="array" ref="L19">ROUND(B19*100*0.7,0)&amp;" EXP + "&amp;ROUND(B19*100*0.7,0)&amp;" PO + "&amp;ROUND(B19*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>5040 EXP + 5040 PO + 50 PARCHEMIN</v>
-      </c>
-      <c r="M19" s="10"/>
-    </row>
-    <row r="20" ht="44.05" customHeight="1">
-      <c r="A20" t="s" s="12">
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" ht="79" customHeight="1">
+      <c r="A20" t="s" s="14">
         <v>72</v>
       </c>
-      <c r="B20" t="s" s="9">
-        <v>111</v>
-      </c>
-      <c r="C20" t="s" s="10">
+      <c r="B20" t="s" s="11">
+        <v>104</v>
+      </c>
+      <c r="C20" t="s" s="12">
         <v>73</v>
       </c>
-      <c r="D20" t="s" s="10">
+      <c r="D20" t="s" s="12">
         <v>74</v>
       </c>
-      <c r="E20" t="s" s="10">
+      <c r="E20" t="s" s="12">
         <v>75</v>
       </c>
-      <c r="F20" t="s" s="10">
+      <c r="F20" t="s" s="12">
         <v>76</v>
       </c>
-      <c r="G20" t="s" s="10">
-        <v>109</v>
-      </c>
-      <c r="H20" t="s" s="10">
-        <v>112</v>
-      </c>
-      <c r="I20" t="s" s="10">
+      <c r="G20" t="s" s="12">
+        <v>103</v>
+      </c>
+      <c r="H20" t="s" s="12">
+        <v>105</v>
+      </c>
+      <c r="I20" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="J20" s="11" cm="1">
+      <c r="J20" s="13" cm="1">
         <f t="array" ref="J20">100*B20</f>
         <v>8100</v>
       </c>
-      <c r="K20" s="11" cm="1">
+      <c r="K20" s="13" cm="1">
         <f t="array" ref="K20">ROUND(40*(B20*0.5),0)</f>
         <v>1620</v>
       </c>
-      <c r="L20" t="str" s="10" cm="1">
-        <f t="array" ref="L20">ROUND(B20*100*0.7,0)&amp;" EXP + "&amp;ROUND(B20*100*0.7,0)&amp;" PO + "&amp;ROUND(B20*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>5670 EXP + 5670 PO + 57 PARCHEMIN</v>
-      </c>
-      <c r="M20" s="10"/>
-    </row>
-    <row r="21" ht="44.05" customHeight="1">
-      <c r="A21" t="s" s="12">
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21" ht="79" customHeight="1">
+      <c r="A21" t="s" s="14">
         <v>79</v>
       </c>
-      <c r="B21" t="s" s="9">
-        <v>114</v>
-      </c>
-      <c r="C21" t="s" s="10">
+      <c r="B21" t="s" s="11">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s" s="12">
         <v>80</v>
       </c>
-      <c r="D21" t="s" s="10">
+      <c r="D21" t="s" s="12">
         <v>81</v>
       </c>
-      <c r="E21" t="s" s="10">
+      <c r="E21" t="s" s="12">
         <v>82</v>
       </c>
-      <c r="F21" t="s" s="10">
+      <c r="F21" t="s" s="12">
         <v>83</v>
       </c>
-      <c r="G21" t="s" s="10">
-        <v>115</v>
-      </c>
-      <c r="H21" t="s" s="10">
-        <v>116</v>
-      </c>
-      <c r="I21" t="s" s="10">
+      <c r="G21" t="s" s="12">
+        <v>107</v>
+      </c>
+      <c r="H21" t="s" s="12">
+        <v>108</v>
+      </c>
+      <c r="I21" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="J21" s="11" cm="1">
+      <c r="J21" s="13" cm="1">
         <f t="array" ref="J21">100*B21</f>
         <v>9000</v>
       </c>
-      <c r="K21" s="11" cm="1">
+      <c r="K21" s="13" cm="1">
         <f t="array" ref="K21">ROUND(40*(B21*0.5),0)</f>
         <v>1800</v>
       </c>
-      <c r="L21" t="str" s="10" cm="1">
-        <f t="array" ref="L21">ROUND(B21*100*0.7,0)&amp;" EXP + "&amp;ROUND(B21*100*0.7,0)&amp;" PO + "&amp;ROUND(B21*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>6300 EXP + 6300 PO + 63 PARCHEMIN</v>
-      </c>
-      <c r="M21" s="10"/>
-    </row>
-    <row r="22" ht="44.05" customHeight="1">
-      <c r="A22" t="s" s="12">
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+    </row>
+    <row r="22" ht="79" customHeight="1">
+      <c r="A22" t="s" s="14">
         <v>86</v>
       </c>
-      <c r="B22" t="s" s="9">
+      <c r="B22" t="s" s="11">
         <v>20</v>
       </c>
-      <c r="C22" t="s" s="10">
+      <c r="C22" t="s" s="12">
         <v>88</v>
       </c>
-      <c r="D22" t="s" s="10">
+      <c r="D22" t="s" s="12">
         <v>89</v>
       </c>
-      <c r="E22" t="s" s="10">
+      <c r="E22" t="s" s="12">
         <v>90</v>
       </c>
-      <c r="F22" t="s" s="10">
+      <c r="F22" t="s" s="12">
         <v>91</v>
       </c>
-      <c r="G22" t="s" s="10">
-        <v>115</v>
-      </c>
-      <c r="H22" t="s" s="10">
-        <v>118</v>
-      </c>
-      <c r="I22" t="s" s="10">
+      <c r="G22" t="s" s="12">
+        <v>107</v>
+      </c>
+      <c r="H22" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="I22" t="s" s="12">
         <v>48</v>
       </c>
-      <c r="J22" s="11" cm="1">
+      <c r="J22" s="13" cm="1">
         <f t="array" ref="J22">100*B22</f>
         <v>10000</v>
       </c>
-      <c r="K22" s="11" cm="1">
+      <c r="K22" s="13" cm="1">
         <f t="array" ref="K22">ROUND(40*(B22*0.5),0)</f>
         <v>2000</v>
       </c>
-      <c r="L22" t="str" s="10" cm="1">
-        <f t="array" ref="L22">ROUND(B22*100*0.7,0)&amp;" EXP + "&amp;ROUND(B22*100*0.7,0)&amp;" PO + "&amp;ROUND(B22*1*0.7,0)&amp;" PARCHEMIN"</f>
-        <v>7000 EXP + 7000 PO + 70 PARCHEMIN</v>
-      </c>
-      <c r="M22" s="10"/>
-    </row>
-    <row r="23" ht="32.05" customHeight="1">
-      <c r="A23" t="s" s="13">
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+    </row>
+    <row r="23" ht="57.5" customHeight="1">
+      <c r="A23" t="s" s="15">
         <v>14</v>
       </c>
-      <c r="B23" t="s" s="9">
-        <v>120</v>
-      </c>
-      <c r="C23" t="s" s="10">
+      <c r="B23" t="s" s="11">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s" s="12">
         <v>15</v>
       </c>
-      <c r="D23" t="s" s="10">
+      <c r="D23" t="s" s="12">
         <v>16</v>
       </c>
-      <c r="E23" t="s" s="10">
+      <c r="E23" t="s" s="12">
         <v>17</v>
       </c>
-      <c r="F23" t="s" s="10">
+      <c r="F23" t="s" s="12">
         <v>18</v>
       </c>
-      <c r="G23" t="s" s="10">
+      <c r="G23" t="s" s="12">
         <v>15</v>
       </c>
-      <c r="H23" t="s" s="10">
+      <c r="H23" t="s" s="12">
         <v>70</v>
       </c>
-      <c r="I23" t="s" s="10">
+      <c r="I23" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J23" s="11" cm="1">
+      <c r="J23" s="13" cm="1">
         <f t="array" ref="J23">100*B23</f>
         <v>20000</v>
       </c>
-      <c r="K23" s="11" cm="1">
+      <c r="K23" s="13" cm="1">
         <f t="array" ref="K23">ROUND(40*(B23*0.3),0)</f>
         <v>2400</v>
       </c>
-      <c r="L23" t="str" s="10" cm="1">
-        <f t="array" ref="L23">ROUND(B23*100*0.4,0)&amp;" EXP + "&amp;ROUND(B23*100*0.4,0)&amp;" PO + "&amp;ROUND(B23*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>8000 EXP + 8000 PO + 80 PARCHEMIN</v>
-      </c>
-      <c r="M23" s="10"/>
-    </row>
-    <row r="24" ht="32.05" customHeight="1">
-      <c r="A24" t="s" s="13">
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+    </row>
+    <row r="24" ht="57.5" customHeight="1">
+      <c r="A24" t="s" s="15">
         <v>22</v>
       </c>
-      <c r="B24" t="s" s="9">
-        <v>122</v>
-      </c>
-      <c r="C24" t="s" s="10">
+      <c r="B24" t="s" s="11">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s" s="12">
         <v>24</v>
       </c>
-      <c r="D24" t="s" s="10">
+      <c r="D24" t="s" s="12">
         <v>25</v>
       </c>
-      <c r="E24" t="s" s="10">
+      <c r="E24" t="s" s="12">
         <v>26</v>
       </c>
-      <c r="F24" t="s" s="10">
+      <c r="F24" t="s" s="12">
         <v>27</v>
       </c>
-      <c r="G24" t="s" s="10">
+      <c r="G24" t="s" s="12">
         <v>15</v>
       </c>
-      <c r="H24" t="s" s="10">
+      <c r="H24" t="s" s="12">
         <v>77</v>
       </c>
-      <c r="I24" t="s" s="10">
+      <c r="I24" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J24" s="11" cm="1">
+      <c r="J24" s="13" cm="1">
         <f t="array" ref="J24">100*B24</f>
         <v>23000</v>
       </c>
-      <c r="K24" s="11" cm="1">
+      <c r="K24" s="13" cm="1">
         <f t="array" ref="K24">ROUND(40*(B24*0.3),0)</f>
         <v>2760</v>
       </c>
-      <c r="L24" t="str" s="10" cm="1">
-        <f t="array" ref="L24">ROUND(B24*100*0.4,0)&amp;" EXP + "&amp;ROUND(B24*100*0.4,0)&amp;" PO + "&amp;ROUND(B24*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>9200 EXP + 9200 PO + 92 PARCHEMIN</v>
-      </c>
-      <c r="M24" s="10"/>
-    </row>
-    <row r="25" ht="32.05" customHeight="1">
-      <c r="A25" t="s" s="13">
-        <v>98</v>
-      </c>
-      <c r="B25" t="s" s="9">
-        <v>124</v>
-      </c>
-      <c r="C25" t="s" s="10">
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+    </row>
+    <row r="25" ht="57.5" customHeight="1">
+      <c r="A25" t="s" s="15">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s" s="11">
+        <v>112</v>
+      </c>
+      <c r="C25" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="D25" t="s" s="10">
+      <c r="D25" t="s" s="12">
         <v>33</v>
       </c>
-      <c r="E25" t="s" s="10">
+      <c r="E25" t="s" s="12">
         <v>34</v>
       </c>
-      <c r="F25" t="s" s="10">
+      <c r="F25" t="s" s="12">
         <v>35</v>
       </c>
-      <c r="G25" t="s" s="10">
-        <v>125</v>
-      </c>
-      <c r="H25" t="s" s="10">
+      <c r="G25" t="s" s="12">
+        <v>113</v>
+      </c>
+      <c r="H25" t="s" s="12">
         <v>84</v>
       </c>
-      <c r="I25" t="s" s="10">
+      <c r="I25" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J25" s="11" cm="1">
+      <c r="J25" s="13" cm="1">
         <f t="array" ref="J25">100*B25</f>
         <v>26000</v>
       </c>
-      <c r="K25" s="11" cm="1">
+      <c r="K25" s="13" cm="1">
         <f t="array" ref="K25">ROUND(40*(B25*0.3),0)</f>
         <v>3120</v>
       </c>
-      <c r="L25" t="str" s="10" cm="1">
-        <f t="array" ref="L25">ROUND(B25*100*0.4,0)&amp;" EXP + "&amp;ROUND(B25*100*0.4,0)&amp;" PO + "&amp;ROUND(B25*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>10400 EXP + 10400 PO + 104 PARCHEMIN</v>
-      </c>
-      <c r="M25" s="10"/>
-    </row>
-    <row r="26" ht="32.05" customHeight="1">
-      <c r="A26" t="s" s="13">
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+    </row>
+    <row r="26" ht="57.5" customHeight="1">
+      <c r="A26" t="s" s="15">
         <v>39</v>
       </c>
-      <c r="B26" t="s" s="9">
-        <v>127</v>
-      </c>
-      <c r="C26" t="s" s="10">
+      <c r="B26" t="s" s="11">
+        <v>114</v>
+      </c>
+      <c r="C26" t="s" s="12">
         <v>41</v>
       </c>
-      <c r="D26" t="s" s="10">
+      <c r="D26" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="E26" t="s" s="10">
+      <c r="E26" t="s" s="12">
         <v>43</v>
       </c>
-      <c r="F26" t="s" s="10">
+      <c r="F26" t="s" s="12">
         <v>44</v>
       </c>
-      <c r="G26" t="s" s="10">
-        <v>125</v>
-      </c>
-      <c r="H26" t="s" s="10">
+      <c r="G26" t="s" s="12">
+        <v>113</v>
+      </c>
+      <c r="H26" t="s" s="12">
         <v>92</v>
       </c>
-      <c r="I26" t="s" s="10">
+      <c r="I26" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="J26" s="11" cm="1">
+      <c r="J26" s="13" cm="1">
         <f t="array" ref="J26">100*B26</f>
         <v>30000</v>
       </c>
-      <c r="K26" s="11" cm="1">
+      <c r="K26" s="13" cm="1">
         <f t="array" ref="K26">ROUND(40*(B26*0.3),0)</f>
         <v>3600</v>
       </c>
-      <c r="L26" t="str" s="10" cm="1">
-        <f t="array" ref="L26">ROUND(B26*100*0.4,0)&amp;" EXP + "&amp;ROUND(B26*100*0.4,0)&amp;" PO + "&amp;ROUND(B26*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>12000 EXP + 12000 PO + 120 PARCHEMIN</v>
-      </c>
-      <c r="M26" s="10"/>
-    </row>
-    <row r="27" ht="32.05" customHeight="1">
-      <c r="A27" t="s" s="13">
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+    </row>
+    <row r="27" ht="57.5" customHeight="1">
+      <c r="A27" t="s" s="15">
         <v>47</v>
       </c>
-      <c r="B27" t="s" s="9">
-        <v>129</v>
-      </c>
-      <c r="C27" t="s" s="10">
+      <c r="B27" t="s" s="11">
+        <v>115</v>
+      </c>
+      <c r="C27" t="s" s="12">
         <v>49</v>
       </c>
-      <c r="D27" t="s" s="10">
+      <c r="D27" t="s" s="12">
         <v>50</v>
       </c>
-      <c r="E27" t="s" s="10">
+      <c r="E27" t="s" s="12">
         <v>51</v>
       </c>
-      <c r="F27" t="s" s="10">
+      <c r="F27" t="s" s="12">
         <v>52</v>
       </c>
-      <c r="G27" t="s" s="10">
+      <c r="G27" t="s" s="12">
         <v>24</v>
       </c>
-      <c r="H27" t="s" s="10">
-        <v>112</v>
-      </c>
-      <c r="I27" t="s" s="10">
+      <c r="H27" t="s" s="12">
+        <v>105</v>
+      </c>
+      <c r="I27" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J27" s="11" cm="1">
+      <c r="J27" s="13" cm="1">
         <f t="array" ref="J27">100*B27</f>
         <v>35000</v>
       </c>
-      <c r="K27" s="11" cm="1">
+      <c r="K27" s="13" cm="1">
         <f t="array" ref="K27">ROUND(40*(B27*0.3),0)</f>
         <v>4200</v>
       </c>
-      <c r="L27" t="str" s="10" cm="1">
-        <f t="array" ref="L27">ROUND(B27*100*0.4,0)&amp;" EXP + "&amp;ROUND(B27*100*0.4,0)&amp;" PO + "&amp;ROUND(B27*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>14000 EXP + 14000 PO + 140 PARCHEMIN</v>
-      </c>
-      <c r="M27" s="10"/>
-    </row>
-    <row r="28" ht="32.05" customHeight="1">
-      <c r="A28" t="s" s="13">
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28" ht="57.5" customHeight="1">
+      <c r="A28" t="s" s="15">
         <v>56</v>
       </c>
-      <c r="B28" t="s" s="9">
-        <v>131</v>
-      </c>
-      <c r="C28" t="s" s="10">
+      <c r="B28" t="s" s="11">
+        <v>116</v>
+      </c>
+      <c r="C28" t="s" s="12">
         <v>58</v>
       </c>
-      <c r="D28" t="s" s="10">
+      <c r="D28" t="s" s="12">
         <v>59</v>
       </c>
-      <c r="E28" t="s" s="10">
+      <c r="E28" t="s" s="12">
         <v>60</v>
       </c>
-      <c r="F28" t="s" s="10">
+      <c r="F28" t="s" s="12">
         <v>61</v>
       </c>
-      <c r="G28" t="s" s="10">
+      <c r="G28" t="s" s="12">
         <v>24</v>
       </c>
-      <c r="H28" t="s" s="10">
-        <v>116</v>
-      </c>
-      <c r="I28" t="s" s="10">
+      <c r="H28" t="s" s="12">
+        <v>108</v>
+      </c>
+      <c r="I28" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J28" s="11" cm="1">
+      <c r="J28" s="13" cm="1">
         <f t="array" ref="J28">100*B28</f>
         <v>40000</v>
       </c>
-      <c r="K28" s="11" cm="1">
+      <c r="K28" s="13" cm="1">
         <f t="array" ref="K28">ROUND(40*(B28*0.3),0)</f>
         <v>4800</v>
       </c>
-      <c r="L28" t="str" s="10" cm="1">
-        <f t="array" ref="L28">ROUND(B28*100*0.4,0)&amp;" EXP + "&amp;ROUND(B28*100*0.4,0)&amp;" PO + "&amp;ROUND(B28*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>16000 EXP + 16000 PO + 160 PARCHEMIN</v>
-      </c>
-      <c r="M28" s="10"/>
-    </row>
-    <row r="29" ht="32.05" customHeight="1">
-      <c r="A29" t="s" s="13">
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+    </row>
+    <row r="29" ht="57.5" customHeight="1">
+      <c r="A29" t="s" s="15">
         <v>64</v>
       </c>
-      <c r="B29" t="s" s="9">
-        <v>133</v>
-      </c>
-      <c r="C29" t="s" s="10">
+      <c r="B29" t="s" s="11">
+        <v>117</v>
+      </c>
+      <c r="C29" t="s" s="12">
         <v>65</v>
       </c>
-      <c r="D29" t="s" s="10">
+      <c r="D29" t="s" s="12">
         <v>66</v>
       </c>
-      <c r="E29" t="s" s="10">
+      <c r="E29" t="s" s="12">
         <v>67</v>
       </c>
-      <c r="F29" t="s" s="10">
+      <c r="F29" t="s" s="12">
         <v>68</v>
       </c>
-      <c r="G29" t="s" s="10">
-        <v>134</v>
-      </c>
-      <c r="H29" t="s" s="10">
+      <c r="G29" t="s" s="12">
         <v>118</v>
       </c>
-      <c r="I29" t="s" s="10">
+      <c r="H29" t="s" s="12">
+        <v>109</v>
+      </c>
+      <c r="I29" t="s" s="12">
         <v>53</v>
       </c>
-      <c r="J29" s="11" cm="1">
+      <c r="J29" s="13" cm="1">
         <f t="array" ref="J29">100*B29</f>
         <v>45000</v>
       </c>
-      <c r="K29" s="11" cm="1">
+      <c r="K29" s="13" cm="1">
         <f t="array" ref="K29">ROUND(40*(B29*0.3),0)</f>
         <v>5400</v>
       </c>
-      <c r="L29" t="str" s="10" cm="1">
-        <f t="array" ref="L29">ROUND(B29*100*0.4,0)&amp;" EXP + "&amp;ROUND(B29*100*0.4,0)&amp;" PO + "&amp;ROUND(B29*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>18000 EXP + 18000 PO + 180 PARCHEMIN</v>
-      </c>
-      <c r="M29" s="10"/>
-    </row>
-    <row r="30" ht="44.05" customHeight="1">
-      <c r="A30" t="s" s="13">
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+    </row>
+    <row r="30" ht="79" customHeight="1">
+      <c r="A30" t="s" s="15">
         <v>72</v>
       </c>
-      <c r="B30" t="s" s="9">
-        <v>136</v>
-      </c>
-      <c r="C30" t="s" s="10">
+      <c r="B30" t="s" s="11">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s" s="12">
         <v>73</v>
       </c>
-      <c r="D30" t="s" s="10">
+      <c r="D30" t="s" s="12">
         <v>74</v>
       </c>
-      <c r="E30" t="s" s="10">
+      <c r="E30" t="s" s="12">
         <v>75</v>
       </c>
-      <c r="F30" t="s" s="10">
+      <c r="F30" t="s" s="12">
         <v>76</v>
       </c>
-      <c r="G30" t="s" s="10">
-        <v>134</v>
-      </c>
-      <c r="H30" t="s" s="10">
-        <v>137</v>
-      </c>
-      <c r="I30" t="s" s="10">
+      <c r="G30" t="s" s="12">
+        <v>118</v>
+      </c>
+      <c r="H30" t="s" s="12">
+        <v>120</v>
+      </c>
+      <c r="I30" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="J30" s="11" cm="1">
+      <c r="J30" s="13" cm="1">
         <f t="array" ref="J30">100*B30</f>
         <v>50000</v>
       </c>
-      <c r="K30" s="11" cm="1">
+      <c r="K30" s="13" cm="1">
         <f t="array" ref="K30">ROUND(40*(B30*0.3),0)</f>
         <v>6000</v>
       </c>
-      <c r="L30" t="str" s="10" cm="1">
-        <f t="array" ref="L30">ROUND(B30*100*0.4,0)&amp;" EXP + "&amp;ROUND(B30*100*0.4,0)&amp;" PO + "&amp;ROUND(B30*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>20000 EXP + 20000 PO + 200 PARCHEMIN</v>
-      </c>
-      <c r="M30" s="10"/>
-    </row>
-    <row r="31" ht="44.05" customHeight="1">
-      <c r="A31" t="s" s="13">
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+    </row>
+    <row r="31" ht="79" customHeight="1">
+      <c r="A31" t="s" s="15">
         <v>79</v>
       </c>
-      <c r="B31" t="s" s="9">
-        <v>139</v>
-      </c>
-      <c r="C31" t="s" s="10">
+      <c r="B31" t="s" s="11">
+        <v>121</v>
+      </c>
+      <c r="C31" t="s" s="12">
         <v>80</v>
       </c>
-      <c r="D31" t="s" s="10">
+      <c r="D31" t="s" s="12">
         <v>81</v>
       </c>
-      <c r="E31" t="s" s="10">
+      <c r="E31" t="s" s="12">
         <v>82</v>
       </c>
-      <c r="F31" t="s" s="10">
+      <c r="F31" t="s" s="12">
         <v>83</v>
       </c>
-      <c r="G31" t="s" s="10">
+      <c r="G31" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="H31" t="s" s="10">
-        <v>140</v>
-      </c>
-      <c r="I31" t="s" s="10">
+      <c r="H31" t="s" s="12">
+        <v>122</v>
+      </c>
+      <c r="I31" t="s" s="12">
         <v>40</v>
       </c>
-      <c r="J31" s="11" cm="1">
+      <c r="J31" s="13" cm="1">
         <f t="array" ref="J31">100*B31</f>
         <v>55000</v>
       </c>
-      <c r="K31" s="11" cm="1">
+      <c r="K31" s="13" cm="1">
         <f t="array" ref="K31">ROUND(40*(B31*0.3),0)</f>
         <v>6600</v>
       </c>
-      <c r="L31" t="str" s="10" cm="1">
-        <f t="array" ref="L31">ROUND(B31*100*0.4,0)&amp;" EXP + "&amp;ROUND(B31*100*0.4,0)&amp;" PO + "&amp;ROUND(B31*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>22000 EXP + 22000 PO + 220 PARCHEMIN</v>
-      </c>
-      <c r="M31" s="10"/>
-    </row>
-    <row r="32" ht="44.05" customHeight="1">
-      <c r="A32" t="s" s="13">
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+    </row>
+    <row r="32" ht="79" customHeight="1">
+      <c r="A32" t="s" s="15">
         <v>86</v>
       </c>
-      <c r="B32" t="s" s="9">
-        <v>142</v>
-      </c>
-      <c r="C32" t="s" s="10">
+      <c r="B32" t="s" s="11">
+        <v>123</v>
+      </c>
+      <c r="C32" t="s" s="12">
         <v>88</v>
       </c>
-      <c r="D32" t="s" s="10">
+      <c r="D32" t="s" s="12">
         <v>89</v>
       </c>
-      <c r="E32" t="s" s="10">
+      <c r="E32" t="s" s="12">
         <v>90</v>
       </c>
-      <c r="F32" t="s" s="10">
+      <c r="F32" t="s" s="12">
         <v>91</v>
       </c>
-      <c r="G32" t="s" s="10">
+      <c r="G32" t="s" s="12">
         <v>32</v>
       </c>
-      <c r="H32" t="s" s="10">
-        <v>143</v>
-      </c>
-      <c r="I32" t="s" s="10">
+      <c r="H32" t="s" s="12">
+        <v>124</v>
+      </c>
+      <c r="I32" t="s" s="12">
         <v>48</v>
       </c>
-      <c r="J32" s="11" cm="1">
+      <c r="J32" s="13" cm="1">
         <f t="array" ref="J32">100*B32</f>
         <v>60000</v>
       </c>
-      <c r="K32" s="11" cm="1">
+      <c r="K32" s="13" cm="1">
         <f t="array" ref="K32">ROUND(40*(B32*0.3),0)</f>
         <v>7200</v>
       </c>
-      <c r="L32" t="str" s="10" cm="1">
-        <f t="array" ref="L32">ROUND(B32*100*0.4,0)&amp;" EXP + "&amp;ROUND(B32*100*0.4,0)&amp;" PO + "&amp;ROUND(B32*1*0.4,0)&amp;" PARCHEMIN"</f>
-        <v>24000 EXP + 24000 PO + 240 PARCHEMIN</v>
-      </c>
-      <c r="M32" s="10"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
     </row>
     <row r="33" ht="116.05" customHeight="1">
-      <c r="A33" t="s" s="14">
-        <v>145</v>
-      </c>
-      <c r="B33" t="s" s="9">
-        <v>146</v>
-      </c>
-      <c r="C33" t="s" s="10">
+      <c r="A33" t="s" s="16">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s" s="11">
+        <v>126</v>
+      </c>
+      <c r="C33" t="s" s="12">
         <v>19</v>
       </c>
-      <c r="D33" t="s" s="10">
-        <v>147</v>
-      </c>
-      <c r="E33" t="s" s="10">
-        <v>148</v>
-      </c>
-      <c r="F33" t="s" s="10">
-        <v>149</v>
-      </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="11" cm="1">
+      <c r="D33" t="s" s="12">
+        <v>127</v>
+      </c>
+      <c r="E33" t="s" s="12">
+        <v>128</v>
+      </c>
+      <c r="F33" t="s" s="12">
+        <v>129</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="13" cm="1">
         <f t="array" ref="J33">100*B33</f>
         <v>100000</v>
       </c>
-      <c r="K33" s="11" cm="1">
+      <c r="K33" s="13" cm="1">
         <f t="array" ref="K33">ROUND(40*(B33*0.3),0)</f>
         <v>12000</v>
       </c>
-      <c r="L33" t="s" s="10">
-        <v>150</v>
-      </c>
-      <c r="M33" t="s" s="10">
-        <v>151</v>
+      <c r="L33" t="s" s="12">
+        <v>130</v>
+      </c>
+      <c r="M33" t="s" s="12">
+        <v>131</v>
       </c>
     </row>
     <row r="34" ht="20.05" customHeight="1">
-      <c r="A34" s="15"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
     </row>
     <row r="35" ht="20.05" customHeight="1">
-      <c r="A35" s="15"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
     </row>
     <row r="36" ht="20.05" customHeight="1">
-      <c r="A36" s="15"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
     </row>
     <row r="37" ht="20.05" customHeight="1">
-      <c r="A37" s="15"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
     </row>
     <row r="38" ht="20.05" customHeight="1">
-      <c r="A38" s="15"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
     </row>
     <row r="39" ht="20.05" customHeight="1">
-      <c r="A39" s="15"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
     </row>
     <row r="40" ht="20.05" customHeight="1">
-      <c r="A40" s="15"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
     </row>
     <row r="41" ht="20.05" customHeight="1">
-      <c r="A41" s="15"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
     </row>
     <row r="42" ht="20.05" customHeight="1">
-      <c r="A42" s="15"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="12"/>
     </row>
     <row r="43" ht="20.05" customHeight="1">
-      <c r="A43" s="15"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
     </row>
     <row r="44" ht="20.05" customHeight="1">
-      <c r="A44" s="15"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
     </row>
     <row r="45" ht="20.05" customHeight="1">
-      <c r="A45" s="15"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
     </row>
     <row r="46" ht="20.05" customHeight="1">
-      <c r="A46" s="15"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
     </row>
     <row r="47" ht="20.05" customHeight="1">
-      <c r="A47" s="15"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
     </row>
     <row r="48" ht="20.05" customHeight="1">
-      <c r="A48" s="15"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
     </row>
     <row r="49" ht="20.05" customHeight="1">
-      <c r="A49" s="15"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
     </row>
     <row r="50" ht="20.05" customHeight="1">
-      <c r="A50" s="15"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
     </row>
     <row r="51" ht="20.05" customHeight="1">
-      <c r="A51" s="15"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
     </row>
     <row r="52" ht="20.05" customHeight="1">
-      <c r="A52" s="15"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
     </row>
     <row r="53" ht="20.05" customHeight="1">
-      <c r="A53" s="15"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
     </row>
     <row r="54" ht="20.05" customHeight="1">
-      <c r="A54" s="15"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
     </row>
     <row r="55" ht="20.05" customHeight="1">
-      <c r="A55" s="15"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12"/>
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
     </row>
     <row r="56" ht="20.05" customHeight="1">
-      <c r="A56" s="15"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
     </row>
     <row r="57" ht="20.05" customHeight="1">
-      <c r="A57" s="15"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
     </row>
     <row r="58" ht="20.05" customHeight="1">
-      <c r="A58" s="15"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="12"/>
+      <c r="M58" s="12"/>
     </row>
     <row r="59" ht="20.05" customHeight="1">
-      <c r="A59" s="15"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
     </row>
     <row r="60" ht="20.05" customHeight="1">
-      <c r="A60" s="15"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="12"/>
+      <c r="M60" s="12"/>
     </row>
     <row r="61" ht="20.05" customHeight="1">
-      <c r="A61" s="15"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
     </row>
     <row r="62" ht="20.05" customHeight="1">
-      <c r="A62" s="15"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
     </row>
     <row r="63" ht="20.05" customHeight="1">
-      <c r="A63" s="15"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
+      <c r="M63" s="12"/>
     </row>
     <row r="64" ht="20.05" customHeight="1">
-      <c r="A64" s="15"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="12"/>
     </row>
     <row r="65" ht="20.05" customHeight="1">
-      <c r="A65" s="15"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="12"/>
+      <c r="L65" s="12"/>
+      <c r="M65" s="12"/>
     </row>
     <row r="66" ht="20.05" customHeight="1">
-      <c r="A66" s="15"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
     </row>
     <row r="67" ht="20.05" customHeight="1">
-      <c r="A67" s="15"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
     </row>
     <row r="68" ht="20.05" customHeight="1">
-      <c r="A68" s="15"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+      <c r="L68" s="12"/>
+      <c r="M68" s="12"/>
     </row>
     <row r="69" ht="20.05" customHeight="1">
-      <c r="A69" s="15"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
     </row>
     <row r="70" ht="20.05" customHeight="1">
-      <c r="A70" s="15"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
     </row>
     <row r="71" ht="20.05" customHeight="1">
-      <c r="A71" s="15"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="10"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
     </row>
     <row r="72" ht="20.05" customHeight="1">
-      <c r="A72" s="15"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
-      <c r="M72" s="10"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="12"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="12"/>
     </row>
     <row r="73" ht="20.05" customHeight="1">
-      <c r="A73" s="15"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="10"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="10"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="12"/>
+      <c r="L73" s="12"/>
+      <c r="M73" s="12"/>
     </row>
     <row r="74" ht="20.05" customHeight="1">
-      <c r="A74" s="15"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="12"/>
     </row>
     <row r="75" ht="20.05" customHeight="1">
-      <c r="A75" s="15"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
+      <c r="K75" s="12"/>
+      <c r="L75" s="12"/>
+      <c r="M75" s="12"/>
     </row>
     <row r="76" ht="20.05" customHeight="1">
-      <c r="A76" s="15"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="10"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="12"/>
     </row>
     <row r="77" ht="20.05" customHeight="1">
-      <c r="A77" s="15"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="10"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="10"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
+      <c r="M77" s="12"/>
     </row>
     <row r="78" ht="20.05" customHeight="1">
-      <c r="A78" s="15"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
+      <c r="M78" s="12"/>
     </row>
     <row r="79" ht="20.05" customHeight="1">
-      <c r="A79" s="15"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
+      <c r="M79" s="12"/>
     </row>
     <row r="80" ht="20.05" customHeight="1">
-      <c r="A80" s="15"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="10"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="10"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="12"/>
+      <c r="L80" s="12"/>
+      <c r="M80" s="12"/>
     </row>
     <row r="81" ht="20.05" customHeight="1">
-      <c r="A81" s="15"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="10"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
+      <c r="M81" s="12"/>
     </row>
     <row r="82" ht="20.05" customHeight="1">
-      <c r="A82" s="15"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="10"/>
-      <c r="M82" s="10"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="12"/>
+      <c r="L82" s="12"/>
+      <c r="M82" s="12"/>
     </row>
     <row r="83" ht="20.05" customHeight="1">
-      <c r="A83" s="15"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="10"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
+      <c r="K83" s="12"/>
+      <c r="L83" s="12"/>
+      <c r="M83" s="12"/>
     </row>
     <row r="84" ht="20.05" customHeight="1">
-      <c r="A84" s="15"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="10"/>
+      <c r="A84" s="17"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="12"/>
+      <c r="L84" s="12"/>
+      <c r="M84" s="12"/>
     </row>
     <row r="85" ht="20.05" customHeight="1">
-      <c r="A85" s="15"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
+      <c r="A85" s="17"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="12"/>
+      <c r="K85" s="12"/>
+      <c r="L85" s="12"/>
+      <c r="M85" s="12"/>
     </row>
     <row r="86" ht="20.05" customHeight="1">
-      <c r="A86" s="15"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10"/>
+      <c r="A86" s="17"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12"/>
+      <c r="I86" s="12"/>
+      <c r="J86" s="12"/>
+      <c r="K86" s="12"/>
+      <c r="L86" s="12"/>
+      <c r="M86" s="12"/>
     </row>
     <row r="87" ht="20.05" customHeight="1">
-      <c r="A87" s="15"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="10"/>
+      <c r="A87" s="17"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="12"/>
+      <c r="K87" s="12"/>
+      <c r="L87" s="12"/>
+      <c r="M87" s="12"/>
     </row>
     <row r="88" ht="20.05" customHeight="1">
-      <c r="A88" s="15"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10"/>
-      <c r="H88" s="10"/>
-      <c r="I88" s="10"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="10"/>
+      <c r="A88" s="17"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12"/>
+      <c r="I88" s="12"/>
+      <c r="J88" s="12"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12"/>
+      <c r="M88" s="12"/>
     </row>
     <row r="89" ht="20.05" customHeight="1">
-      <c r="A89" s="15"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="10"/>
+      <c r="A89" s="17"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="12"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="12"/>
+      <c r="I89" s="12"/>
+      <c r="J89" s="12"/>
+      <c r="K89" s="12"/>
+      <c r="L89" s="12"/>
+      <c r="M89" s="12"/>
     </row>
     <row r="90" ht="20.05" customHeight="1">
-      <c r="A90" s="15"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="10"/>
-      <c r="M90" s="10"/>
+      <c r="A90" s="17"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+      <c r="H90" s="12"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="12"/>
+      <c r="K90" s="12"/>
+      <c r="L90" s="12"/>
+      <c r="M90" s="12"/>
     </row>
     <row r="91" ht="20.05" customHeight="1">
-      <c r="A91" s="15"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
+      <c r="A91" s="17"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="12"/>
+      <c r="I91" s="12"/>
+      <c r="J91" s="12"/>
+      <c r="K91" s="12"/>
+      <c r="L91" s="12"/>
+      <c r="M91" s="12"/>
     </row>
     <row r="92" ht="20.05" customHeight="1">
-      <c r="A92" s="15"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
+      <c r="A92" s="17"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="12"/>
+      <c r="K92" s="12"/>
+      <c r="L92" s="12"/>
+      <c r="M92" s="12"/>
     </row>
     <row r="93" ht="20.05" customHeight="1">
-      <c r="A93" s="15"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="10"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="10"/>
+      <c r="A93" s="17"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
+      <c r="M93" s="12"/>
     </row>
     <row r="94" ht="20.05" customHeight="1">
-      <c r="A94" s="15"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="A94" s="17"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
+      <c r="M94" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/donjons.xlsx
+++ b/docs/donjons.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="133">
   <si>
     <t>Tableau 1</t>
   </si>
@@ -333,7 +333,7 @@
     <t>M1M1M1M1M1EM2M2M2M2M2EM23M23M23M23M23EM3M3M3M3M3M3EM34M34M34M34B</t>
   </si>
   <si>
-    <t>Démon supérieur, chien infernal, mage noir, slime chromatique</t>
+    <t>Démon supérieur, chien infernal, ange déchu, slime chromatique</t>
   </si>
   <si>
     <t>Myhrra, démon ultime (très résistant à tout, attaques de feu physique très puissantes, haut CRT)</t>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>39,39,22</t>
+  </si>
+  <si>
+    <t>Démon supérieur, chien infernal, mage noir, slime chromatique</t>
   </si>
   <si>
     <t>37,38,25</t>
@@ -2664,7 +2667,7 @@
         <v>89</v>
       </c>
       <c r="E22" t="s" s="12">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s" s="12">
         <v>91</v>
@@ -2673,7 +2676,7 @@
         <v>107</v>
       </c>
       <c r="H22" t="s" s="12">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I22" t="s" s="12">
         <v>48</v>
@@ -2694,7 +2697,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s" s="12">
         <v>15</v>
@@ -2733,7 +2736,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s" s="11">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s" s="12">
         <v>24</v>
@@ -2772,7 +2775,7 @@
         <v>96</v>
       </c>
       <c r="B25" t="s" s="11">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s" s="12">
         <v>32</v>
@@ -2787,7 +2790,7 @@
         <v>35</v>
       </c>
       <c r="G25" t="s" s="12">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H25" t="s" s="12">
         <v>84</v>
@@ -2811,7 +2814,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s" s="11">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s" s="12">
         <v>41</v>
@@ -2826,7 +2829,7 @@
         <v>44</v>
       </c>
       <c r="G26" t="s" s="12">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H26" t="s" s="12">
         <v>92</v>
@@ -2850,7 +2853,7 @@
         <v>47</v>
       </c>
       <c r="B27" t="s" s="11">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s" s="12">
         <v>49</v>
@@ -2889,7 +2892,7 @@
         <v>56</v>
       </c>
       <c r="B28" t="s" s="11">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s" s="12">
         <v>58</v>
@@ -2928,7 +2931,7 @@
         <v>64</v>
       </c>
       <c r="B29" t="s" s="11">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s" s="12">
         <v>65</v>
@@ -2943,10 +2946,10 @@
         <v>68</v>
       </c>
       <c r="G29" t="s" s="12">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H29" t="s" s="12">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I29" t="s" s="12">
         <v>53</v>
@@ -2967,7 +2970,7 @@
         <v>72</v>
       </c>
       <c r="B30" t="s" s="11">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s" s="12">
         <v>73</v>
@@ -2982,10 +2985,10 @@
         <v>76</v>
       </c>
       <c r="G30" t="s" s="12">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H30" t="s" s="12">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I30" t="s" s="12">
         <v>40</v>
@@ -3006,7 +3009,7 @@
         <v>79</v>
       </c>
       <c r="B31" t="s" s="11">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s" s="12">
         <v>80</v>
@@ -3024,7 +3027,7 @@
         <v>32</v>
       </c>
       <c r="H31" t="s" s="12">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I31" t="s" s="12">
         <v>40</v>
@@ -3045,7 +3048,7 @@
         <v>86</v>
       </c>
       <c r="B32" t="s" s="11">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s" s="12">
         <v>88</v>
@@ -3054,7 +3057,7 @@
         <v>89</v>
       </c>
       <c r="E32" t="s" s="12">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s" s="12">
         <v>91</v>
@@ -3063,7 +3066,7 @@
         <v>32</v>
       </c>
       <c r="H32" t="s" s="12">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I32" t="s" s="12">
         <v>48</v>
@@ -3081,22 +3084,22 @@
     </row>
     <row r="33" ht="116.05" customHeight="1">
       <c r="A33" t="s" s="16">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" t="s" s="11">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s" s="12">
         <v>19</v>
       </c>
       <c r="D33" t="s" s="12">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s" s="12">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" t="s" s="12">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
@@ -3110,10 +3113,10 @@
         <v>12000</v>
       </c>
       <c r="L33" t="s" s="12">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M33" t="s" s="12">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" ht="20.05" customHeight="1">
